--- a/src/main/resources/excel_0/1. Job.xlsx
+++ b/src/main/resources/excel_0/1. Job.xlsx
@@ -2354,6 +2354,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2374,6 +2375,7 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2423,15 +2425,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2561,503 +2563,503 @@
   <dimension ref="A1:D91"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="43.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="86.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="36.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="2" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="2" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="2" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="2" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="2" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="A71" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="D72" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="D73" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
+    <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="D74" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
+    <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="D75" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="s">
+    <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D76" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="s">
+    <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="D77" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="s">
+    <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="D78" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="s">
+    <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="D79" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="s">
+    <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D80" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="s">
+    <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="D81" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
+    <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="D82" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="s">
+    <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="D83" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="s">
+    <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="D84" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="s">
+    <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="D85" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="s">
+    <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="D86" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="s">
+    <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B87" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="D87" s="2" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1" t="s">
+    <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B88" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="D88" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="s">
+    <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="D89" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="s">
+    <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B90" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="D90" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="s">
+    <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="D91" s="2" t="s">
         <v>122</v>
       </c>
     </row>
@@ -3080,427 +3082,427 @@
   <dimension ref="A1:A87"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="51.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="84.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="44.51"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="2" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="2" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="2" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="2" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="2" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="2" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="2" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="2" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="2" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="2" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="2" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="2" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="2" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="2" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="2" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="2" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="2" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="2" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="2" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="2" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="2" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="2" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="2" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="2" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="2" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="2" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="2" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="2" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="2" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="2" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="2" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="2" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="2" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="2" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="2" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="2" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="s">
+      <c r="A68" s="2" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="s">
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="s">
+      <c r="A70" s="2" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="2" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="2" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="2" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="2" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="s">
+      <c r="A76" s="2" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="s">
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="s">
+      <c r="A78" s="2" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="2" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="s">
+      <c r="A80" s="2" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="s">
+      <c r="A81" s="2" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
+      <c r="A82" s="2" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="s">
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="s">
+      <c r="A84" s="2" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="s">
+      <c r="A85" s="2" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="s">
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="s">
+      <c r="A87" s="2" t="s">
         <v>206</v>
       </c>
     </row>
@@ -3523,426 +3525,426 @@
   <dimension ref="A1:A87"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="81.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="81.56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="2" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="2" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="2" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="2" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="2" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="2" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="2" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="2" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="2" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="2" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="2" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="2" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="2" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="2" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="2" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="2" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="2" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="2" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="2" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="2" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="2" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="2" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="2" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="2" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="2" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="2" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="2" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="2" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="2" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="2" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="2" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="2" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="2" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="2" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="2" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="2" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="2" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="2" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="2" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="2" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="2" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="s">
+      <c r="A68" s="2" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="2" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="s">
+      <c r="A70" s="2" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="2" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="2" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="2" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
+      <c r="A74" s="2" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="2" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="s">
+      <c r="A76" s="2" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="s">
+      <c r="A77" s="2" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="s">
+      <c r="A78" s="2" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="2" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="s">
+      <c r="A80" s="2" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="s">
+      <c r="A81" s="2" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
+      <c r="A82" s="2" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="s">
+      <c r="A83" s="2" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="s">
+      <c r="A84" s="2" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="s">
+      <c r="A85" s="2" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="s">
+      <c r="A86" s="2" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="s">
+      <c r="A87" s="2" t="s">
         <v>290</v>
       </c>
     </row>
@@ -3965,7 +3967,7 @@
   <dimension ref="A1:A109"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="118.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="118.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4074,422 +4076,422 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="2" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="2" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="2" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="2" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="2" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="2" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="2" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="2" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="2" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="2" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="2" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="2" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="2" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="2" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="2" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="2" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="2" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="2" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="2" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="2" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="2" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="2" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="2" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="2" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="2" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="2" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="2" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="2" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="2" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="2" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="2" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="2" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="2" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="2" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="2" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="2" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="2" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="2" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="2" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="2" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="2" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="s">
+      <c r="A68" s="2" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="2" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="s">
+      <c r="A70" s="2" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="2" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="2" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="2" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
+      <c r="A74" s="2" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="2" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="s">
+      <c r="A76" s="2" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="s">
+      <c r="A77" s="2" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="s">
+      <c r="A78" s="2" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="2" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="s">
+      <c r="A80" s="2" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="s">
+      <c r="A81" s="2" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
+      <c r="A82" s="2" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="s">
+      <c r="A83" s="2" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="s">
+      <c r="A84" s="2" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="s">
+      <c r="A85" s="2" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="s">
+      <c r="A86" s="2" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="s">
+      <c r="A87" s="2" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="s">
+      <c r="A89" s="2" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="s">
+      <c r="A90" s="2" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="s">
+      <c r="A91" s="2" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="s">
+      <c r="A92" s="2" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
+      <c r="A93" s="2" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1" t="s">
+      <c r="A94" s="2" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="s">
+      <c r="A95" s="2" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1" t="s">
+      <c r="A96" s="2" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="s">
+      <c r="A97" s="2" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1" t="s">
+      <c r="A98" s="2" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1" t="s">
+      <c r="A99" s="2" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1" t="s">
+      <c r="A100" s="2" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="s">
+      <c r="A101" s="2" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="1" t="s">
+      <c r="A102" s="2" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="1" t="s">
+      <c r="A103" s="2" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="1" t="s">
+      <c r="A104" s="2" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1" t="s">
+      <c r="A105" s="2" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="1" t="s">
+      <c r="A106" s="2" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="1" t="s">
+      <c r="A107" s="2" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="1" t="s">
+      <c r="A108" s="2" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="1" t="s">
+      <c r="A109" s="2" t="s">
         <v>395</v>
       </c>
     </row>
@@ -4512,531 +4514,531 @@
   <dimension ref="A1:A109"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="73.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="73.21"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="2" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="2" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="2" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="2" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="2" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="2" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="2" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="2" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="2" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="2" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="2" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="2" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="2" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="2" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="2" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="2" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="2" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="2" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="2" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="2" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="2" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="2" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="2" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="2" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="2" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="2" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="2" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="2" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="2" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="2" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="2" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="2" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="2" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="2" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="2" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="2" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="2" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="2" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="2" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="2" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="2" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="s">
+      <c r="A68" s="2" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="2" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="s">
+      <c r="A70" s="2" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="2" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="2" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="2" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
+      <c r="A74" s="2" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="2" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="s">
+      <c r="A76" s="2" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="s">
+      <c r="A77" s="2" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="s">
+      <c r="A78" s="2" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="2" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="s">
+      <c r="A80" s="2" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="s">
+      <c r="A81" s="2" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
+      <c r="A82" s="2" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="s">
+      <c r="A83" s="2" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="s">
+      <c r="A84" s="2" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="s">
+      <c r="A85" s="2" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="s">
+      <c r="A86" s="2" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="s">
+      <c r="A87" s="2" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="s">
+      <c r="A89" s="2" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="s">
+      <c r="A90" s="2" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="s">
+      <c r="A91" s="2" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="s">
+      <c r="A92" s="2" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
+      <c r="A93" s="2" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1" t="s">
+      <c r="A94" s="2" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="s">
+      <c r="A95" s="2" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1" t="s">
+      <c r="A96" s="2" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="s">
+      <c r="A97" s="2" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1" t="s">
+      <c r="A98" s="2" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1" t="s">
+      <c r="A99" s="2" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1" t="s">
+      <c r="A100" s="2" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="s">
+      <c r="A101" s="2" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="1" t="s">
+      <c r="A102" s="2" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="1" t="s">
+      <c r="A103" s="2" t="s">
         <v>494</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="1" t="s">
+      <c r="A104" s="2" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1" t="s">
+      <c r="A105" s="2" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="1" t="s">
+      <c r="A106" s="2" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="1" t="s">
+      <c r="A107" s="2" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="1" t="s">
+      <c r="A108" s="2" t="s">
         <v>499</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="1" t="s">
+      <c r="A109" s="2" t="s">
         <v>500</v>
       </c>
     </row>
@@ -5059,7 +5061,7 @@
   <dimension ref="A1:A131"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="73.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="73.04"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5168,527 +5170,527 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="2" t="s">
         <v>523</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="2" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="2" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="2" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="2" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="2" t="s">
         <v>529</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="2" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="2" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="2" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="2" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="2" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="2" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="2" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="2" t="s">
         <v>537</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="2" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="2" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="2" t="s">
         <v>540</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="2" t="s">
         <v>541</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="2" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="2" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="2" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="2" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="2" t="s">
         <v>544</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="2" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="2" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="2" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="2" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="2" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="2" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="2" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="2" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="2" t="s">
         <v>552</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="2" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="2" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="2" t="s">
         <v>555</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="2" t="s">
         <v>556</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="2" t="s">
         <v>557</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="2" t="s">
         <v>558</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="2" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="2" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="2" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="s">
+      <c r="A68" s="2" t="s">
         <v>562</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="2" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="s">
+      <c r="A70" s="2" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="2" t="s">
         <v>565</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="2" t="s">
         <v>566</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="2" t="s">
         <v>567</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
+      <c r="A74" s="2" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="2" t="s">
         <v>569</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="s">
+      <c r="A76" s="2" t="s">
         <v>570</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="s">
+      <c r="A77" s="2" t="s">
         <v>571</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="s">
+      <c r="A78" s="2" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="2" t="s">
         <v>573</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="s">
+      <c r="A80" s="2" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="s">
+      <c r="A81" s="2" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
+      <c r="A82" s="2" t="s">
         <v>576</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="s">
+      <c r="A83" s="2" t="s">
         <v>577</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="s">
+      <c r="A84" s="2" t="s">
         <v>578</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="s">
+      <c r="A85" s="2" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="s">
+      <c r="A86" s="2" t="s">
         <v>580</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="s">
+      <c r="A87" s="2" t="s">
         <v>581</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="s">
+      <c r="A89" s="2" t="s">
         <v>582</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="s">
+      <c r="A90" s="2" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="s">
+      <c r="A91" s="2" t="s">
         <v>584</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="s">
+      <c r="A92" s="2" t="s">
         <v>585</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
+      <c r="A93" s="2" t="s">
         <v>586</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1" t="s">
+      <c r="A94" s="2" t="s">
         <v>587</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="s">
+      <c r="A95" s="2" t="s">
         <v>588</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1" t="s">
+      <c r="A96" s="2" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="s">
+      <c r="A97" s="2" t="s">
         <v>590</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1" t="s">
+      <c r="A98" s="2" t="s">
         <v>591</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1" t="s">
+      <c r="A99" s="2" t="s">
         <v>592</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1" t="s">
+      <c r="A100" s="2" t="s">
         <v>593</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="s">
+      <c r="A101" s="2" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="1" t="s">
+      <c r="A102" s="2" t="s">
         <v>595</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="1" t="s">
+      <c r="A103" s="2" t="s">
         <v>596</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="1" t="s">
+      <c r="A104" s="2" t="s">
         <v>597</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1" t="s">
+      <c r="A105" s="2" t="s">
         <v>598</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="1" t="s">
+      <c r="A106" s="2" t="s">
         <v>599</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="1" t="s">
+      <c r="A107" s="2" t="s">
         <v>600</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="1" t="s">
+      <c r="A108" s="2" t="s">
         <v>601</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="1" t="s">
+      <c r="A109" s="2" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="1" t="s">
+      <c r="A111" s="2" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="1" t="s">
+      <c r="A112" s="2" t="s">
         <v>604</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="1" t="s">
+      <c r="A113" s="2" t="s">
         <v>605</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="1" t="s">
+      <c r="A114" s="2" t="s">
         <v>606</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="1" t="s">
+      <c r="A115" s="2" t="s">
         <v>607</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="1" t="s">
+      <c r="A116" s="2" t="s">
         <v>608</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="1" t="s">
+      <c r="A117" s="2" t="s">
         <v>609</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="1" t="s">
+      <c r="A118" s="2" t="s">
         <v>610</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="1" t="s">
+      <c r="A119" s="2" t="s">
         <v>611</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="1" t="s">
+      <c r="A120" s="2" t="s">
         <v>612</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="1" t="s">
+      <c r="A121" s="2" t="s">
         <v>613</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="1" t="s">
+      <c r="A122" s="2" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="1" t="s">
+      <c r="A123" s="2" t="s">
         <v>615</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="1" t="s">
+      <c r="A124" s="2" t="s">
         <v>616</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="1" t="s">
+      <c r="A125" s="2" t="s">
         <v>617</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="1" t="s">
+      <c r="A126" s="2" t="s">
         <v>618</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="1" t="s">
+      <c r="A127" s="2" t="s">
         <v>619</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="1" t="s">
+      <c r="A128" s="2" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="1" t="s">
+      <c r="A129" s="2" t="s">
         <v>621</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="1" t="s">
+      <c r="A130" s="2" t="s">
         <v>622</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="1" t="s">
+      <c r="A131" s="2" t="s">
         <v>623</v>
       </c>
     </row>
@@ -5711,426 +5713,426 @@
   <dimension ref="A1:A87"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="68.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="68.33"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>625</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>626</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>627</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>628</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>629</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>630</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>632</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>633</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>634</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>636</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>637</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>638</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>639</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>640</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>641</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>642</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>643</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>644</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>645</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="2" t="s">
         <v>646</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>647</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="2" t="s">
         <v>648</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="2" t="s">
         <v>649</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="2" t="s">
         <v>650</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="2" t="s">
         <v>651</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="2" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="2" t="s">
         <v>653</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="2" t="s">
         <v>654</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="2" t="s">
         <v>655</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="2" t="s">
         <v>656</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="2" t="s">
         <v>657</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="2" t="s">
         <v>658</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="2" t="s">
         <v>659</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="2" t="s">
         <v>660</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="2" t="s">
         <v>661</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="2" t="s">
         <v>662</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="2" t="s">
         <v>663</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="2" t="s">
         <v>664</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="2" t="s">
         <v>665</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="2" t="s">
         <v>666</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="2" t="s">
         <v>667</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="2" t="s">
         <v>668</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="2" t="s">
         <v>669</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="2" t="s">
         <v>670</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="2" t="s">
         <v>671</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="2" t="s">
         <v>672</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="2" t="s">
         <v>673</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="2" t="s">
         <v>674</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="2" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="2" t="s">
         <v>676</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="2" t="s">
         <v>677</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="2" t="s">
         <v>678</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="2" t="s">
         <v>679</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="2" t="s">
         <v>680</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="2" t="s">
         <v>681</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="2" t="s">
         <v>682</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="2" t="s">
         <v>683</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="2" t="s">
         <v>684</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="2" t="s">
         <v>685</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="2" t="s">
         <v>686</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="2" t="s">
         <v>687</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="s">
+      <c r="A68" s="2" t="s">
         <v>688</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="2" t="s">
         <v>689</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="s">
+      <c r="A70" s="2" t="s">
         <v>690</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="2" t="s">
         <v>691</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="2" t="s">
         <v>692</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="2" t="s">
         <v>693</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
+      <c r="A74" s="2" t="s">
         <v>694</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="2" t="s">
         <v>695</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="s">
+      <c r="A76" s="2" t="s">
         <v>696</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="s">
+      <c r="A77" s="2" t="s">
         <v>697</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="s">
+      <c r="A78" s="2" t="s">
         <v>698</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="2" t="s">
         <v>699</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="s">
+      <c r="A80" s="2" t="s">
         <v>700</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="s">
+      <c r="A81" s="2" t="s">
         <v>701</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
+      <c r="A82" s="2" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="s">
+      <c r="A83" s="2" t="s">
         <v>703</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="s">
+      <c r="A84" s="2" t="s">
         <v>704</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="s">
+      <c r="A85" s="2" t="s">
         <v>705</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="s">
+      <c r="A86" s="2" t="s">
         <v>706</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="s">
+      <c r="A87" s="2" t="s">
         <v>707</v>
       </c>
     </row>
@@ -6153,321 +6155,321 @@
   <dimension ref="A1:A65"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="96.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="96.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>708</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>709</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>711</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>712</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>713</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>714</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>715</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>716</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>717</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>718</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>719</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>720</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>721</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>722</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>723</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>724</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>725</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>726</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>727</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>728</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>729</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="2" t="s">
         <v>730</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>731</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="2" t="s">
         <v>732</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="2" t="s">
         <v>733</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="2" t="s">
         <v>734</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="2" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="2" t="s">
         <v>736</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="2" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="2" t="s">
         <v>738</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="2" t="s">
         <v>739</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="2" t="s">
         <v>740</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="2" t="s">
         <v>741</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="2" t="s">
         <v>742</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="2" t="s">
         <v>743</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="2" t="s">
         <v>744</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="2" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="2" t="s">
         <v>746</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="2" t="s">
         <v>747</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="2" t="s">
         <v>748</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="2" t="s">
         <v>749</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="2" t="s">
         <v>750</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="2" t="s">
         <v>751</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="2" t="s">
         <v>752</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="2" t="s">
         <v>753</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="2" t="s">
         <v>754</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="2" t="s">
         <v>755</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="2" t="s">
         <v>756</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="2" t="s">
         <v>757</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="2" t="s">
         <v>758</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="2" t="s">
         <v>759</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="2" t="s">
         <v>760</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="2" t="s">
         <v>761</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="2" t="s">
         <v>762</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="2" t="s">
         <v>763</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="2" t="s">
         <v>764</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="2" t="s">
         <v>765</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="2" t="s">
         <v>766</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="2" t="s">
         <v>767</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="2" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="2" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="2" t="s">
         <v>770</v>
       </c>
     </row>
